--- a/2026.02.16_Файлы загрузки и выгрузки данных/Загрузочные файлы/Загрузочные данные_четкий RICE_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Загрузочные файлы/Загрузочные данные_четкий RICE_один эксперт.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\2026.02.11_Файлы загрузки и выгрузки\20260218_обновленные файлы\RICE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\79147\Documents\Документы, инвестиции, личные финансы\2024.07.03_Альфа-банк\Магистратура ВШЭ\20_Магистерская диссертация\2026.02.11_Файлы загрузки и выгрузки\2026.04.08_Обновление\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDCCFA67-4888-41E4-ACD1-6E89B03F675C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D00B23F-88D5-4960-A7E5-6751EB7A9126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -122,11 +122,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -419,189 +421,189 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3">
         <v>10000</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>0.6</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="3">
         <v>100</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>3</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>0.9</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="3">
         <v>1000</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>0.8</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
         <v>100</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0.5</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0.7</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="3">
         <v>200</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>0.5</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="3">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="3">
         <v>50</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.8</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>1000</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>0.5</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>0.9</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="3">
         <v>20000</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>0.25</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>0.6</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="3">
         <v>300</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>2</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>0.7</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>3</v>
       </c>
     </row>
